--- a/data/trans_bre/P16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Edad-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,59</t>
+          <t>-0,13; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,15</t>
+          <t>-1,67; -0,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,09</t>
+          <t>-0,73; 1,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,29</t>
+          <t>0,44; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,69</t>
+          <t>0,12; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,99</t>
+          <t>-0,46; 0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,89</t>
+          <t>-0,17; 1,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,19; —</t>
+          <t>-47,59; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,63</t>
+          <t>-1,25; 2,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,39</t>
+          <t>0,18; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,94</t>
+          <t>0,89; 3,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,75</t>
+          <t>0,31; 4,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 268,01</t>
+          <t>-46,03; 253,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 707,65</t>
+          <t>-18,19; 771,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,58; 2051,49</t>
+          <t>55,46; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 615,04</t>
+          <t>12,48; 628,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,32</t>
+          <t>-2,84; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,58</t>
+          <t>3,16; 9,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,3</t>
+          <t>1,01; 6,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,61</t>
+          <t>2,42; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 97,72</t>
+          <t>-29,15; 102,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,79; 519,88</t>
+          <t>64,55; 547,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 495,71</t>
+          <t>15,73; 576,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>69,44; 426,22</t>
+          <t>63,94; 430,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,04</t>
+          <t>5,17; 14,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 15,5</t>
+          <t>5,92; 15,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,71</t>
+          <t>3,25; 9,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 10,5</t>
+          <t>-0,75; 10,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,37; 340,88</t>
+          <t>58,62; 345,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,84; 552,41</t>
+          <t>72,59; 500,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,74; 583,01</t>
+          <t>67,63; 582,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 393,59</t>
+          <t>-10,28; 404,56</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,55</t>
+          <t>-7,95; 5,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 14,49</t>
+          <t>1,95; 15,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 9,28</t>
+          <t>-0,32; 8,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,75</t>
+          <t>4,09; 10,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 39,67</t>
+          <t>-36,63; 40,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 137,74</t>
+          <t>10,11; 159,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 177,06</t>
+          <t>-5,04; 157,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,35; 223,32</t>
+          <t>46,11; 216,68</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,08</t>
+          <t>1,18; 3,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,68</t>
+          <t>2,8; 4,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,27</t>
+          <t>1,66; 3,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,25</t>
+          <t>2,25; 4,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,77; 123,17</t>
+          <t>34,83; 123,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>112,72; 268,35</t>
+          <t>110,35; 274,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,08; 320,14</t>
+          <t>93,59; 309,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>112,42; 307,66</t>
+          <t>115,25; 301,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>139,93%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,51</t>
+          <t>-0,13; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,15</t>
+          <t>-1,54; -0,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,15</t>
+          <t>-0,43; 1,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>196,8%</t>
+          <t>233,2%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,24</t>
+          <t>0,44; 2,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,66</t>
+          <t>0,26; 1,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,98</t>
+          <t>-0,36; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,84</t>
+          <t>-0,05; 1,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,59; —</t>
+          <t>-57,59; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>125,62%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,65</t>
+          <t>-1,03; 2,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,31</t>
+          <t>0,07; 3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,99</t>
+          <t>0,92; 3,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,51</t>
+          <t>-0,74; 2,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 253,16</t>
+          <t>-44,33; 254,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 771,18</t>
+          <t>-16,28; 571,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,46; —</t>
+          <t>51,93; 2125,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 628,53</t>
+          <t>-27,75; 203,95</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>186,43%</t>
+          <t>186,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,29</t>
+          <t>-2,55; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,44</t>
+          <t>3,06; 9,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,18</t>
+          <t>0,69; 6,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,61</t>
+          <t>2,39; 6,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 102,64</t>
+          <t>-26,97; 96,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,55; 547,8</t>
+          <t>58,85; 543,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 576,8</t>
+          <t>8,44; 542,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,94; 430,48</t>
+          <t>63,27; 416,75</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>169,88%</t>
+          <t>319,45%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,35</t>
+          <t>5,1; 14,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 15,6</t>
+          <t>5,99; 15,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,92</t>
+          <t>2,77; 10,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 10,6</t>
+          <t>7,28; 12,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,62; 345,79</t>
+          <t>58,07; 341,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,59; 500,86</t>
+          <t>73,14; 503,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,63; 582,38</t>
+          <t>46,14; 583,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 404,56</t>
+          <t>162,66; 574,57</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>108,22%</t>
+          <t>110,59%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 5,81</t>
+          <t>-7,47; 6,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,57</t>
+          <t>2,19; 15,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 8,71</t>
+          <t>-0,57; 8,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,95</t>
+          <t>4,22; 10,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 40,98</t>
+          <t>-34,75; 44,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,11; 159,37</t>
+          <t>8,63; 150,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 157,76</t>
+          <t>-7,59; 161,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,11; 216,68</t>
+          <t>45,86; 216,7</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>190,69%</t>
+          <t>192,95%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,15</t>
+          <t>1,2; 3,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,7</t>
+          <t>2,84; 4,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,23</t>
+          <t>1,73; 3,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,19</t>
+          <t>2,81; 4,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,83; 123,14</t>
+          <t>34,95; 124,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>110,35; 274,43</t>
+          <t>112,6; 278,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,59; 309,86</t>
+          <t>106,21; 296,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>115,25; 301,29</t>
+          <t>127,79; 277,13</t>
         </is>
       </c>
     </row>
